--- a/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260807.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260807.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>9.79%</t>
+          <t>9.93%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>8.81%</t>
+          <t>8.68%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>5.93%</t>
+          <t>6.04%</t>
         </is>
       </c>
     </row>
@@ -682,24 +682,24 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.24%</t>
+          <t>5.23%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>186,546,000</t>
+          <t>109,474,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -711,22 +711,22 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>109,474,000</t>
+          <t>186,546,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.69%</t>
+          <t>3.57%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.46%</t>
+          <t>3.52%</t>
         </is>
       </c>
     </row>
@@ -765,12 +765,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>27,148,000</t>
+          <t>27,298,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.33%</t>
+          <t>3.37%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.26%</t>
+          <t>3.24%</t>
         </is>
       </c>
     </row>
@@ -809,56 +809,56 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>436,925,000</t>
+          <t>442,925,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.18%</t>
+          <t>3.24%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>202608TX</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>台股期貨</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>2,056</t>
+          <t>361,389,964</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>3.03%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>202608TX</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>台股期貨</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>359,789,964</t>
+          <t>2,056</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.99%</t>
+          <t>3.00%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.81%</t>
+          <t>2.80%</t>
         </is>
       </c>
     </row>
@@ -902,227 +902,227 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.74%</t>
+          <t>2.76%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>63,040,000</t>
+          <t>230,616,516</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.63%</t>
+          <t>2.57%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>82,730,000</t>
+          <t>63,040,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.59%</t>
+          <t>2.57%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>26,144,000</t>
+          <t>202,817,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.57%</t>
+          <t>2.53%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>230,616,516</t>
+          <t>26,144,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.55%</t>
+          <t>2.52%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>145,652,000</t>
+          <t>82,730,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.45%</t>
+          <t>2.50%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>97,953,442</t>
+          <t>145,652,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.45%</t>
+          <t>2.47%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>台灣大</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>202,817,000</t>
+          <t>131,978,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.44%</t>
+          <t>2.43%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>131,978,000</t>
+          <t>97,953,442</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.41%</t>
+          <t>2.32%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>中華電</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>28,764,000</t>
+          <t>99,617,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.29%</t>
+          <t>2.26%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>99,617,000</t>
+          <t>28,764,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.25%</t>
+          <t>2.24%</t>
         </is>
       </c>
     </row>
@@ -1151,39 +1151,39 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>188,180,000</t>
+          <t>55,187,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>2.03%</t>
+          <t>2.01%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>55,187,000</t>
+          <t>273,066,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1195,66 +1195,66 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>273,066,000</t>
+          <t>188,180,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.95%</t>
+          <t>1.99%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>5876</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>上海商銀</t>
+          <t>鈊  象</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>259,999,845</t>
+          <t>14,253,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.86%</t>
+          <t>1.88%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>5876</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>鈊  象</t>
+          <t>上海商銀</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>14,253,000</t>
+          <t>259,999,845</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.84%</t>
+          <t>1.86%</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>1.66%</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>13,886,507,507</t>
+          <t>13,930,374,237</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr"/>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>4,339,382,783</t>
+          <t>4,355,419,583</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr"/>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>-67,350,140</t>
+          <t>-52,184,644</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr"/>
